--- a/public/import_guru_siswa/template_siswa.xlsx
+++ b/public/import_guru_siswa/template_siswa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\SIMPEL-5\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\SIMPEL-5\public\import_guru_siswa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487A9AE5-9C76-408F-9559-8877B6242E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABFF998-3775-4D43-BC68-AA1DC3359650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B5C1236F-2DC1-4DEB-9CB8-AC0626038A09}"/>
   </bookViews>
@@ -60,16 +60,16 @@
     <t>siswa6@gmail.com</t>
   </si>
   <si>
-    <t>Siswa 5</t>
-  </si>
-  <si>
-    <t>Siswa 6</t>
-  </si>
-  <si>
     <t>Multimedia</t>
   </si>
   <si>
     <t>11 MM 1</t>
+  </si>
+  <si>
+    <t>Siswa 5 import</t>
+  </si>
+  <si>
+    <t>Siswa 6 import</t>
   </si>
 </sst>
 </file>
@@ -486,16 +486,16 @@
     </row>
     <row r="2" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2">
         <v>1234500</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2">
         <v>3</v>
@@ -506,16 +506,16 @@
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2">
         <v>1234400</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2">
         <v>3</v>
